--- a/artfynd/A 62085-2020 artfynd.xlsx
+++ b/artfynd/A 62085-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62085-2020 artfynd.xlsx
+++ b/artfynd/A 62085-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4900,10 +4900,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4171948</v>
+        <v>1836667</v>
       </c>
       <c r="B37" t="n">
-        <v>95510</v>
+        <v>77505</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4912,25 +4912,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221944</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4940,10 +4940,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>439761.0104880339</v>
+        <v>440000.6527454211</v>
       </c>
       <c r="R37" t="n">
-        <v>7170955.679539966</v>
+        <v>7170900.345430594</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -5026,10 +5026,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1836667</v>
+        <v>861155</v>
       </c>
       <c r="B38" t="n">
-        <v>77505</v>
+        <v>78569</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5042,21 +5042,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5066,10 +5066,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>440000.6527454211</v>
+        <v>439992.6383284699</v>
       </c>
       <c r="R38" t="n">
-        <v>7170900.345430594</v>
+        <v>7170907.361926482</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5152,10 +5152,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>861155</v>
+        <v>359376</v>
       </c>
       <c r="B39" t="n">
-        <v>78569</v>
+        <v>77667</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5164,25 +5164,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>439992.6383284699</v>
+        <v>440012.8683679985</v>
       </c>
       <c r="R39" t="n">
-        <v>7170907.361926482</v>
+        <v>7170823.8111077</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>359376</v>
+        <v>435729</v>
       </c>
       <c r="B40" t="n">
-        <v>77667</v>
+        <v>73698</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5290,38 +5290,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1249</v>
+        <v>1467</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Vågen-Brännälven, Jmt</t>
+          <t>Klumpens ostsluttning, V om Brännälven,, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>440012.8683679985</v>
+        <v>440137.2059395389</v>
       </c>
       <c r="R40" t="n">
-        <v>7170823.8111077</v>
+        <v>7171013.362353601</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5348,7 +5350,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2009-08-07</t>
+          <t>2003-10-23</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5358,7 +5360,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2009-08-07</t>
+          <t>2003-10-23</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5366,6 +5368,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>ca 200 m V om Styggdalsäckens utlopp i Brännälven,</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5375,39 +5382,35 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
-      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>björkhögstubbe (30 cm dbh),</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr"/>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Hans Sundström</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>Forskningsresan</t>
+          <t>Lst Z Artdatabas</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>435729</v>
+        <v>168368</v>
       </c>
       <c r="B41" t="n">
-        <v>73698</v>
+        <v>73685</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5416,25 +5419,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1467</v>
+        <v>492</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5446,10 +5449,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>440137.2059395389</v>
+        <v>440241.0561405008</v>
       </c>
       <c r="R41" t="n">
-        <v>7171013.362353601</v>
+        <v>7170491.820284128</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5496,7 +5499,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ca 200 m V om Styggdalsäckens utlopp i Brännälven,</t>
+          <t>ca 400 m S om Styggdalsäckens utlopp i Brännälven,</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5508,9 +5511,14 @@
       <c r="AG41" t="b">
         <v>0</v>
       </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>150-årig granskog av högörttyp på ostsluttning,</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>björkhögstubbe (30 cm dbh),</t>
+          <t>på ved i skrymsle vid basen av björkhögstubbe (4 m hög, 20 cm dbh) i glänta</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr"/>
@@ -5533,10 +5541,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>168368</v>
+        <v>176425</v>
       </c>
       <c r="B42" t="n">
-        <v>73685</v>
+        <v>77590</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5545,25 +5553,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>492</v>
+        <v>283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5637,14 +5645,9 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>150-årig granskog av högörttyp på ostsluttning,</t>
-        </is>
-      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>på ved i skrymsle vid basen av björkhögstubbe (4 m hög, 20 cm dbh) i glänta</t>
+          <t>kvist (0,7 cm dia) av levande gran (25 cm dbh),</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr"/>
@@ -5667,10 +5670,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>176425</v>
+        <v>435911</v>
       </c>
       <c r="B43" t="n">
-        <v>77590</v>
+        <v>73698</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5683,21 +5686,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>283</v>
+        <v>1467</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5705,14 +5708,14 @@
       <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Klumpens ostsluttning, V om Brännälven,, Jmt</t>
+          <t>Klumpens NOsluttning, V om Brännälven,, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>440241.0561405008</v>
+        <v>440000.4764794471</v>
       </c>
       <c r="R43" t="n">
-        <v>7170491.820284128</v>
+        <v>7171562.467890644</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5759,7 +5762,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ca 400 m S om Styggdalsäckens utlopp i Brännälven,</t>
+          <t>ca 750 m NNV om Styggdalsäckens utlopp i Brännälven,</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5773,7 +5776,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>kvist (0,7 cm dia) av levande gran (25 cm dbh),</t>
+          <t>bas av gran (35 cm dbh),</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr"/>
@@ -5796,10 +5799,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>435911</v>
+        <v>356281</v>
       </c>
       <c r="B44" t="n">
-        <v>73698</v>
+        <v>77668</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5808,25 +5811,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5834,14 +5837,14 @@
       <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Klumpens NOsluttning, V om Brännälven,, Jmt</t>
+          <t>Klumpens Osluttning, V om Brännälven,, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>440000.4764794471</v>
+        <v>440150.0948786023</v>
       </c>
       <c r="R44" t="n">
-        <v>7171562.467890644</v>
+        <v>7171513.22598121</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5888,7 +5891,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ca 750 m NNV om Styggdalsäckens utlopp i Brännälven,</t>
+          <t>ca 600 m NNV om Styggdalsäckens utlopp i Brännälven,</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5902,7 +5905,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>bas av gran (35 cm dbh),</t>
+          <t>levande lutande björk (40 cm dbh),</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr"/>
@@ -5925,10 +5928,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>356281</v>
+        <v>790681</v>
       </c>
       <c r="B45" t="n">
-        <v>77668</v>
+        <v>78570</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5937,25 +5940,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5963,14 +5966,14 @@
       <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Klumpens Osluttning, V om Brännälven,, Jmt</t>
+          <t>Klumpens ostsluttning, V om Brännälven,, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>440150.0948786023</v>
+        <v>440103.2580735133</v>
       </c>
       <c r="R45" t="n">
-        <v>7171513.22598121</v>
+        <v>7170945.887968294</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -6017,7 +6020,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ca 600 m NNV om Styggdalsäckens utlopp i Brännälven,</t>
+          <t>ca 200 m V om Styggdalsäckens utlopp i Brännälven,</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6031,7 +6034,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>levande lutande björk (40 cm dbh),</t>
+          <t>bark på levande gråal (40 cm dbh),</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr"/>
@@ -6054,10 +6057,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>790681</v>
+        <v>1975192</v>
       </c>
       <c r="B46" t="n">
-        <v>78570</v>
+        <v>78569</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6070,21 +6073,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6160,7 +6163,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>bark på levande gråal (40 cm dbh),</t>
+          <t>Gråal</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr"/>
@@ -6183,10 +6186,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1975192</v>
+        <v>168369</v>
       </c>
       <c r="B47" t="n">
-        <v>78569</v>
+        <v>73685</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6195,25 +6198,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6225,10 +6228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>440103.2580735133</v>
+        <v>440137.2059395389</v>
       </c>
       <c r="R47" t="n">
-        <v>7170945.887968294</v>
+        <v>7171013.362353601</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6289,7 +6292,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Gråal</t>
+          <t>på björkhögstubbe (40 cm dbh),</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr"/>
@@ -6312,10 +6315,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>168369</v>
+        <v>94834792</v>
       </c>
       <c r="B48" t="n">
-        <v>73685</v>
+        <v>76863</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6328,39 +6331,40 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Klumpens ostsluttning, V om Brännälven,, Jmt</t>
+          <t>Klumpen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>440137.2059395389</v>
+        <v>439720.9418674656</v>
       </c>
       <c r="R48" t="n">
-        <v>7171013.362353601</v>
+        <v>7171227.766648524</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6384,7 +6388,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2003-10-23</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6394,7 +6398,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2003-10-23</t>
+          <t>2021-07-07</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6402,46 +6406,32 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>ca 200 m V om Styggdalsäckens utlopp i Brännälven,</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>på björkhögstubbe (40 cm dbh),</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr"/>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Jonny Daborg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Jonny Daborg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>94834792</v>
+        <v>94834362</v>
       </c>
       <c r="B49" t="n">
         <v>76863</v>
@@ -6480,14 +6470,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Klumpen, Jmt</t>
+          <t>Brännälvsravinen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>439720.9418674656</v>
+        <v>440165.3806096307</v>
       </c>
       <c r="R49" t="n">
-        <v>7171227.766648524</v>
+        <v>7170940.8020287</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6541,6 +6531,26 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Mkt grov gammal gran</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies # Mkt grov gammal gran</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6557,10 +6567,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>94834362</v>
+        <v>94834249</v>
       </c>
       <c r="B50" t="n">
-        <v>76863</v>
+        <v>73562</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6569,25 +6579,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>498</v>
+        <v>229654</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6600,10 +6610,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>440165.3806096307</v>
+        <v>440157.5644660502</v>
       </c>
       <c r="R50" t="n">
-        <v>7170940.8020287</v>
+        <v>7170675.64404122</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6658,24 +6668,29 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av triviallöv i ravin med suboceaniskt klimat.</t>
+        </is>
+      </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>skrovellav</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>Mkt grov gammal gran</t>
+          <t>på klen låga av sälg</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies # Mkt grov gammal gran</t>
+          <t>Lobaria scrobiculata # på klen låga av sälg</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6693,7 +6708,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>94834249</v>
+        <v>94834024</v>
       </c>
       <c r="B51" t="n">
         <v>73562</v>
@@ -6736,10 +6751,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>440157.5644660502</v>
+        <v>440109.4687042095</v>
       </c>
       <c r="R51" t="n">
-        <v>7170675.64404122</v>
+        <v>7170912.763045072</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6796,7 +6811,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Gammal granskog med inslag av triviallöv i ravin med suboceaniskt klimat.</t>
+          <t>Gråalskog av högörtstyp (stormhatt, stinknäva etc.) i ravin med suboceaniskt klimat.</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -6811,12 +6826,12 @@
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>på klen låga av sälg</t>
+          <t>På äldre gråal</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata # på klen låga av sälg</t>
+          <t>Lobaria scrobiculata # På äldre gråal</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6834,10 +6849,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>94834024</v>
+        <v>94835088</v>
       </c>
       <c r="B52" t="n">
-        <v>73562</v>
+        <v>77668</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6846,25 +6861,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229654</v>
+        <v>1249</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6873,14 +6888,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Brännälvsravinen, Jmt</t>
+          <t>Klumpen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>440109.4687042095</v>
+        <v>439700.2982610697</v>
       </c>
       <c r="R52" t="n">
-        <v>7170912.763045072</v>
+        <v>7171268.462060122</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6925,6 +6940,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Förekommer med ganska hög frekvens I hela sluttningen.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6934,31 +6954,6 @@
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Gråalskog av högörtstyp (stormhatt, stinknäva etc.) i ravin med suboceaniskt klimat.</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>skrovellav</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>På äldre gråal</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata # På äldre gråal</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6975,10 +6970,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>94835088</v>
+        <v>94835010</v>
       </c>
       <c r="B53" t="n">
-        <v>77668</v>
+        <v>76863</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6991,21 +6986,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1249</v>
+        <v>498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7014,14 +7009,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Klumpen, Jmt</t>
+          <t>Brännälvsravinen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>439700.2982610697</v>
+        <v>439997.4319294745</v>
       </c>
       <c r="R53" t="n">
-        <v>7171268.462060122</v>
+        <v>7171560.385705925</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7064,11 +7059,6 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Förekommer med ganska hög frekvens I hela sluttningen.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7096,10 +7086,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>94835010</v>
+        <v>94834432</v>
       </c>
       <c r="B54" t="n">
-        <v>76863</v>
+        <v>89832</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7112,21 +7102,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>498</v>
+        <v>1209</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7139,10 +7129,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>439997.4319294745</v>
+        <v>440185.0512714045</v>
       </c>
       <c r="R54" t="n">
-        <v>7171560.385705925</v>
+        <v>7170654.955005483</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7212,10 +7202,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>94834432</v>
+        <v>94834694</v>
       </c>
       <c r="B55" t="n">
-        <v>89832</v>
+        <v>77668</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7228,21 +7218,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>1249</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7255,10 +7245,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>440185.0512714045</v>
+        <v>440169.2020800561</v>
       </c>
       <c r="R55" t="n">
-        <v>7170654.955005483</v>
+        <v>7171025.587303917</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7301,6 +7291,11 @@
       <c r="AB55" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Förekommer med hög frekvens i västra sluttningen i ravinen</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7328,10 +7323,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>94834694</v>
+        <v>94834909</v>
       </c>
       <c r="B56" t="n">
-        <v>77668</v>
+        <v>76863</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7344,21 +7339,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1249</v>
+        <v>498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7367,14 +7362,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Brännälvsravinen, Jmt</t>
+          <t>Klumpen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>440169.2020800561</v>
+        <v>439838.5470872348</v>
       </c>
       <c r="R56" t="n">
-        <v>7171025.587303917</v>
+        <v>7171078.427874464</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7419,11 +7414,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Förekommer med hög frekvens i västra sluttningen i ravinen</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7446,122 +7436,6 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>94834909</v>
-      </c>
-      <c r="B57" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>498</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Liten sotlav</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Acolium karelicum</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Klumpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>439838.5470872348</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7171078.427874464</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Frostviken</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2021-07-07</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Jonny Daborg</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Jonny Daborg</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
